--- a/全流程时间轴法规整理.xlsx
+++ b/全流程时间轴法规整理.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="12800" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="201">
+  <si>
+    <t>阶段</t>
+  </si>
   <si>
     <r>
       <rPr>
@@ -20736,13 +20739,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -21411,9 +21414,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -21421,15 +21421,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21441,13 +21444,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21812,918 +21815,920 @@
     </row>
     <row r="2" customHeight="1" spans="1:30">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="U2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
       <c r="Z2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AC2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="409.5" customHeight="1" spans="1:30">
       <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="H3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
       <c r="T3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AD3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:30">
       <c r="A4" s="1"/>
-      <c r="B4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4"/>
       <c r="E4" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="Q4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="3"/>
+      <c r="R4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="4"/>
       <c r="T4" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X4" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AB4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="AD4" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" ht="266" spans="1:30">
       <c r="A5" s="1"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="3"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="I5" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="J5" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="S5" s="3"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S5" s="4"/>
       <c r="T5" s="10"/>
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
       <c r="W5" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
-      <c r="Z5" s="5" t="s">
-        <v>54</v>
+      <c r="Z5" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="AA5" s="10"/>
       <c r="AB5" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" ht="406" spans="1:30">
       <c r="A6" s="1"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>42</v>
+      <c r="H6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="S6" s="3"/>
+      <c r="O6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="S6" s="4"/>
       <c r="T6" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>54</v>
+        <v>85</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD6" s="5" t="s">
-        <v>54</v>
+        <v>89</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:30">
       <c r="A7" s="1"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q7" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="Q7" s="5"/>
       <c r="R7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="S7" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="S7" s="4"/>
       <c r="T7" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC7" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>54</v>
+        <v>112</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="409.5" customHeight="1" spans="1:30">
       <c r="A8" s="1"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
+      <c r="D8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="T8" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>54</v>
+        <v>127</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC8" s="5" t="s">
-        <v>54</v>
+        <v>132</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="AD8" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:30">
       <c r="A9" s="1"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3" t="s">
-        <v>133</v>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="5" t="s">
         <v>144</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="T9" s="10"/>
       <c r="U9" s="10"/>
       <c r="V9" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA9" s="5" t="s">
-        <v>54</v>
+        <v>150</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC9" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="AD9" s="5" t="s">
-        <v>54</v>
+        <v>152</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="406" spans="1:30">
       <c r="A10" s="1"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="N10" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="N10" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="Q10" s="4"/>
+      <c r="O10" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q10" s="5"/>
       <c r="R10" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="S10" s="3"/>
+        <v>165</v>
+      </c>
+      <c r="S10" s="4"/>
       <c r="T10" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB10" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB10" s="4"/>
       <c r="AC10" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD10" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="1"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="3" t="s">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="L11" s="5"/>
+      <c r="M11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="N11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="5" t="s">
-        <v>6</v>
+      <c r="O11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
       <c r="Z11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AC11" s="5" t="s">
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD11" s="5" t="s">
+      <c r="AC11" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="AD11" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:30">
       <c r="A12" s="1"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="U12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="V12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="W12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="X12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="Y12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="Z12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="AA12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="AB12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="AC12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="U12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="W12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="X12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC12" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="AD12" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="214" customHeight="1" spans="1:30">
       <c r="A13" s="1"/>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="Q13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="S13" s="4"/>
+      <c r="T13" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="X13" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD13" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="Q13" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="S13" s="3"/>
-      <c r="T13" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="X13" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y13" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z13" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="14" ht="238" spans="1:30">
       <c r="A14" s="1"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3" t="s">
-        <v>186</v>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>42</v>
+        <v>189</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>42</v>
+        <v>190</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
       <c r="Q14" s="14"/>
       <c r="R14" s="14"/>
       <c r="S14" s="15"/>
@@ -22741,29 +22746,29 @@
     </row>
     <row r="15" customHeight="1" spans="1:30">
       <c r="A15" s="1"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="D15" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
       <c r="M15" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>42</v>
+        <v>194</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
@@ -22782,27 +22787,27 @@
     </row>
     <row r="16" ht="406" spans="1:30">
       <c r="A16" s="1"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
       <c r="M16" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>42</v>
+        <v>196</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q16" s="14"/>
       <c r="R16" s="14"/>
@@ -22821,22 +22826,22 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" s="1"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
       <c r="Q17" s="14"/>
       <c r="R17" s="14"/>
       <c r="S17" s="15"/>
@@ -22854,22 +22859,22 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" s="1"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
       <c r="Q18" s="14"/>
       <c r="R18" s="14"/>
       <c r="S18" s="15"/>
@@ -22887,43 +22892,43 @@
     </row>
     <row r="19" ht="308" spans="1:30">
       <c r="A19" s="1"/>
-      <c r="B19" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="3"/>
+      <c r="B19" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M19" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M19" s="4"/>
       <c r="N19" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
